--- a/data/species-base/Cyrtosperma-pages.xlsx
+++ b/data/species-base/Cyrtosperma-pages.xlsx
@@ -438,16 +438,16 @@
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="80" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="90" customWidth="1" min="17" max="17"/>
-    <col width="90" customWidth="1" min="18" max="18"/>
+    <col width="80" customWidth="1" min="17" max="17"/>
+    <col width="80" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
   </cols>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1606</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,8 @@
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Cyrtosperma johnstonii (W.Bull ex T.Moore &amp; Mast.) N.E.Br., published in The Gardeners' Chronicle n.s. 18: 808 (23 December 1882).
-Alocasia johnstonii W.Bull ex T.Moore &amp; Mast., Gardeners' Chronicle n.s. 5: 603 (6 May 1876), in the report of Mr Bull's six new plants at the Brussels exhibition: "a species having purple, mottled stalks, furnished with short prickles arranged in groups, and arrow-shaped, erect, dark green leaves veined with red", said to come from New Guinea.¹² Hay (1988) had taken Bull's 1878 retail list as the place of publication and chose a Kew sheet as lectotype;⁴ Hay (2020) showed the basionym was validly published in 1876 and neotypified it.⁵
+Alocasia johnstonii W.Bull ex T.Moore &amp; Mast., Gardeners' Chronicle n.s. 5: 603 (6 May 1876), in the report of Mr Bull's six new plants at the Brussels exhibition: "a species having purple, mottled stalks, furnished with short prickles arranged in groups, and arrow-shaped, erect, dark green leaves veined with red", said to come from New Guinea.¹² Hay (1988) had taken Bull's 1878 retail list as the place of publication and chose as lectotype the sterile leaves Bull sent to Kew in September 1878 (K000499264);⁴ Hay (2020) showed that the 1876 report, four months earlier than Wittmack's account of the same exhibition, validly published the basionym, so that the Kew sheet is not original material and a neotype was needed.⁵
+Neotype: D.H. Nicolson 976, 3 May 1961, cultivated in the Bogor Botanic Garden, West Java, plant II.Q.F.35 (US, two sheets, barcodes 03822207 and 03822208; isoneotypes BO, L), designated by Hay (2020).⁵ Hay cites the basionym as Alocasia johnstonii W.Bull ex Mast.; IPNI and POWO credit the unsigned 1876 report to the Chronicle's editors, T. Moore and M.T. Masters, and that form is used here.¹ ⁵ Masters printed the epithet as "johnsoni" and Bull always as "johnstoni", an orthographic error corrected to johnstonii under the Code.⁵
 N.E. Brown's 1882 note records the first flowering in Europe, at the Compagnie Continentale d'Horticulture, Ghent, of the plant "which Mr. W. Bull introduced from the Solomon Isles, and sent out as Alocasia Johnstoni": peduncle like the petiole and armed with clusters of spines in an interrupted spiral; spathe ovate-lanceolate, acuminate, slightly convolute at the base, about 5 inches long, apparently brownish; spadix 2 inches by a quarter inch, brownish, flowering from the apex downwards; perianth of six free segments; six free stamens with exserted white anthers; ovary ovoid-oblong, one-celled, with two or sometimes one anatropous ovule fixed to the side of the cell. He calls it "the first Cyrtosperma that has been cultivated in European gardens".²</t>
         </is>
       </c>
@@ -733,7 +734,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Known for a century only from cultivation and said to have come from the Solomon Islands; the one field record Hay could find was a juvenile from open country at Hapan on Buka Island, labelled Caladium.⁴ The first wild-collected specimens were gathered in 2013 in the New Georgia group, Western Province, Solomon Islands.⁵ Herbarium records otherwise come from botanic gardens on four continents.⁶</t>
+          <t>Known for over a century only from cultivation. Bull's exhibit of 1876 was labelled as introduced from New Guinea in 1875, but from 1878 his catalogues gave the Solomon Islands, and that origin was repeated without corroboration ever since; the one field record Hay could find in 1988 was a juvenile from open country at Hapan on Buka Island, labelled Caladium, "a very optimistic connection at best".⁴ ⁵ The first wild-collected specimens are two juveniles gathered in 2013 by the National Museum of Natural Science, Taiwan, with the Solomon Islands forestry ministry, in the New Georgia group of Western Province: Hsu et al. SITW03642, beside a stream near Zaira village on Vangunu Island, and Yang et al. SITW01542, in forest at Sanapro village on Vella Lavella Island (TNM), both at very low elevation and both with the pink venation and incipient combs of upturned prickles of the species.⁵ A plant photographed by Patrick Blanc at Tenaru Falls on Guadalcanal in 2019 has the combed prickles but grows as a solitary-leaved forest-understorey plant, and may be something new.⁵ Herbarium records otherwise come from botanic gardens on four continents.⁶</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -743,12 +744,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Peduncle similar to but shorter than the petioles. Spathe deeply and narrowly boat-shaped, 9 to c. 40 cm long, rather abruptly more deeply and narrowly concave in the upper portion, erect, dark purple outside, pale dirty yellowish green within; spadix 7–25 cm long, with a short free stipe, somewhat glaucous; flowers hexamerous; anthers exserted at male anthesis; ovary 1–2-ovulate. Fruit and seed unknown to Hay in 1988;⁴ fertility is the subject of Hay's 2020 note.⁵</t>
+          <t>Peduncle similar to but shorter than the petioles. Spathe deeply and narrowly boat-shaped, 9 to c. 40 cm long, rather abruptly more deeply and narrowly concave in the upper portion, erect, dark purple outside, pale dirty yellowish green within; spadix 7–25 cm long, with a short free stipe, somewhat glaucous; flowers hexamerous; anthers exserted at male anthesis; ovary 1–2-ovulate. Fruit and seed were unknown to Hay in 1988;⁴ fruiting plants have since been photographed in the Singapore Botanic Gardens (February 2019) and at Tully in North Queensland: an immature fruiting spadix c. 15 cm long on a collapsed peduncle, with the almost black remnant of the spathe persisting, purple-black tepals between the berries, and the berries ripening from the tip of the spadix downwards and turning yellow.⁵</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Lowland; the Buka juvenile came from open country and the 2013 collections from the New Georgia group.⁴ ⁵ In cultivation grown both as a terrestrial and as an aquatic, the aquatic plants the larger.⁷</t>
+          <t>Lowland. The two 2013 collections are from a streamside and from forest at very low elevation, and the Buka juvenile from open country.⁴ ⁵ In cultivation the plant thrives as a helophyte in submerged mud: at Bogor it grew far better as an emergent aquatic than as a terrestrial plant, with petioles alone reaching 2.5 m, and Hay doubts that it is a forest-understorey plant at all.⁵ ⁷</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -758,16 +759,17 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Named by William Bull's nursery for a Johnston who is not identified in the 1876 report or in Brown's 1882 note; the spelling Johnstoni was corrected to johnstonii under the Code.</t>
+          <t>Named by William Bull's nursery for a Johnston whose identity remains unknown: a search by Hay, David Mabberley and Lex Thomson in 2020 reached no conclusion.⁵ Masters printed the epithet "johnsoni" and Bull consistently "johnstoni", an orthographic error corrected to johnstonii under the Code, as Wittmack (1876) and Beccari (1885) already had it.⁵</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>1. Introduced by William Bull of Chelsea in the 1870s, exhibited at Brussels in 1876 as an Alocasia "from New Guinea", figured in colour by André in 1880 as Alocasia Johnstoni,⁸ and first flowered in Europe at Ghent in 1882.² Brown published it again with a plate and description in the Botanical Magazine in 1914, calling it the only Cyrtosperma then in cultivation.⁹
+          <t>1. Introduced to European cultivation by William Bull of King's Road, Chelsea, in 1875; exhibited as "Alocasia johnstoni" at the centenary exhibition of the Société Royale de Flore in Brussels in 1876, where Bull's new plants took the top gold medal, and again at Carlisle in 1877; first offered for sale in his catalogue of 1878; figured in colour by André in 1880, who suggested it might be a Lasia;⁸ and first flowered at the Compagnie Continentale d'Horticulture in Ghent in 1882, when Brown, who had suspected a Cyrtosperma from the leaves sent to Kew in 1878, received the bloom on 11 December and published the new combination twelve days later.² ⁵ Beccari's Cyrtosperma johnstonii of 1885 is an isonym.⁵ Brown published the species again with a plate and description in the Botanical Magazine in 1914, calling it the only Cyrtosperma then in cultivation.⁹
 2. Phenotypically very variable with age and treatment: young plants show the brilliant pink costae, well-grown ones the dark blotching beneath, and an established clump carries the whole range of inflorescence sizes at once among crowns of different sizes.⁴
-3. Diploid, 2n = 26.¹⁰ The inflorescences are protogynous and self-sterile, and plants bearing several at once fail to set seed, so Hay concluded the species is either sterile or physiologically self-sterile and that all cultivated plants are probably a single clone.⁴ Hay (2020) revisits origin and fertility with the wild material now known.⁵
+3. Diploid, 2n = 26.¹⁰ The inflorescences are protogynous and self-sterile, and plants bearing several at once fail to set seed, so Hay concluded in 1988 that the species is either sterile or physiologically self-sterile and that all cultivated plants are probably a single clone.⁴ In 2020 he showed that it does fruit, at Singapore and at Tully; that the diploid count rules out a sterile triploid, though not in principle a sterile diploid hybrid; and that its now-known wild occurrence makes sterility unlikely. Each bloom is mechanically self-incompatible, since pollen is shed only after all the stigmas have ceased to be receptive, and the rarity of fruit even where several blooms are open together suggests that the clonally identical cultivated plants are genetically self-incompatible as well.⁵
 4. "Widely distributed in living botanical collections, but too slow growing to be of much commercial horticultural interest" was Hay's verdict in 1988;⁴ it is now a sought-after collectors' plant and most iNaturalist records are of cultivated specimens.³
-5. A traditional medicine in Thailand; its flavonoid glycosides, rutin and isorhamnetin-3-O-rutinoside, and their hydrolysis products show antioxidant, antiproliferative and anti-inflammatory activity in vitro.¹¹</t>
+5. A traditional medicine in Thailand; its flavonoid glycosides, rutin and isorhamnetin-3-O-rutinoside, and their hydrolysis products show antioxidant, antiproliferative and anti-inflammatory activity in vitro.¹¹
+6. Hay (2020) counts at least three species in the Solomons archipelago, C. johnstonii, C. bougainvillense and C. merkusii, the last both as prickly wild plants and as gigantic, more or less unarmed edible forms, and two single-island endemics in the Louisiades, and expects more island endemics to turn up in the western Pacific.⁵</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -776,7 +778,7 @@
 2. Brown, N.E. 1882. Cyrtosperma Johnstoni, N.E.Br. Gardeners' Chronicle n.s. 18: 808 — protologue of the combination. https://archive.org/details/gardenerschronic18lond
 3. iNaturalist: Cyrtosperma johnstonii. https://www.inaturalist.org/taxa/344195
 4. Hay, A. 1988. Cyrtosperma (Araceae) and its Old World allies. Blumea 33: 427–469. https://repository.naturalis.nl/pub/526134
-5. Hay, A. 2020. Notes on the typification, origin, and fertility of Cyrtosperma johnstonii (Araceae–Lasioideae). Aroideana 43(3–4): 108.
+5. Hay, A. 2020. Notes on the typification, origin, and fertility of Cyrtosperma johnstonii (Araceae–Lasioideae). Aroideana 43(3–4): 108–117.
 6. GBIF occurrence download for Cyrtosperma, 2026-09-05 (60 records). https://www.gbif.org/species/2871907
 7. Alderwerelt van Rosenburgh, C.R.W.K. van. 1920. New or noteworthy Malayan Araceae II. Bulletin du Jardin Botanique de Buitenzorg sér. 3, 1: 373. https://archive.org/details/bulletindelinsti20kebu
 8. André, E. 1880. Alocasia Johnstoni. L'Illustration Horticole 27: 133–134, Pl. CCCXCV. https://www.biodiversitylibrary.org/page/15949217
@@ -792,7 +794,7 @@
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1029</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="4">
@@ -906,7 +908,7 @@
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>980</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1023,7 @@
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>1105</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="6">
@@ -1047,13 +1049,13 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>hero from inat/giganteum (three observations, 2025–2026, one wild); no type image online (BO); Hay 1988 Fig. 3 map</t>
+          <t>hero from inat/giganteum (three observations, 2025–2026, one wild); the first published photographs of the living plant are Imran's four figures in Hay &amp; Imran 2020 (Aroideana 43(3–4), on the Drive); no type image online (BO); Hay 1988 Fig. 3 map</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Cyrtosperma giganteum Engl., published in Nova Guinea 8(1): 249 (1910), in Engler &amp; Krause's Araceae of the Lorentz expedition.
-Type: Versteeg 1818, Papua, Lorentz (Noord) River, flowering October 1907 (lectotype BO, chosen by Hay 1988); Versteeg 1141, May 1907, is the other original gathering.
+Type: Versteeg 1818, Papua, Noord (Lorentz) River, flowering October 1907 (lectotype BO, chosen by Hay 1988); Versteeg 1141, May 1907 (BO, L), is the other original gathering, and Engler also cited von Römer 193 of 1909, which has not been located.⁴ ⁶
 Translated from protologue: Leaf with petiole to 2.5 m long, the adult blade coriaceous, ovate-sagittate, the anterior lobe to about 75 cm long and 70 cm wide at the base, obtuse or apiculate at the apex, the posterior lobes to 1 m or more long and 50 cm wide, bent back, subacute, separated by a deep acute sinus, with about eight distant primary lateral nerves joined into a marginal collective vein, the posterior costae bare in the sinus for about 10 cm. Peduncle to 4.5 cm in diameter, smooth. Spathe ovate-lanceolate with a long acumen, reddish brown, convolute below, about 8 cm across and about 35 cm or more long; spadix dark rose, stipitate for 2 cm, 21 cm long and about 4 cm thick. Stamens 4–5, 3 mm long, on filaments up to 1 mm. Pistil 4 mm long, the ovary with several ovules. Perianth of 4–5 tepals 3.5 mm long. Fruiting spadix to 36 cm long and 9 cm thick. Berries ellipsoid, green, 1.5 cm long and 6 mm thick. Seeds several.²</t>
         </is>
       </c>
@@ -1079,22 +1081,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>The Lorentz River basin of southern Papua, where Hay knew it only from Versteeg's two gatherings and Engler's unlocated von Römer 193;⁴ R.J. Johns and colleagues collected it there again in the 1990s, and there are records from Western Province, Papua New Guinea.⁵ Rediscovered in the field by Hay &amp; Imran (2020).⁶</t>
+          <t>Indonesia, Papua Province, in the Mimika and Asmat Regencies of the southern lowlands.⁶ First collected in 1907 by G.M. Versteeg and again in 1909 by L.S.A.M. von Römer on the Noord River, renamed the Lorentz in 1910 and now the Unir of the Asmat people; Hay knew it only from those gatherings.⁴ There was then no scientific record for over ninety years, until R.J. Johns collected it in 1999 and 2000 on the Freeport concession in the Mimika Regency (Johns 9831 and 10638, K), an encounter published only as the habit photograph that illustrates the genus on POWO, and Imran photographed it near Timika in 2020.⁶ GBIF also lists specimens from Western Province, Papua New Guinea, which Hay &amp; Imran do not cite.⁵</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>A huge plant, poorly known. Leaves with the petiole to 2.5 m long, the blade unarmed and the upper petiole unarmed, the lower part armed with scattered straight spines; blade coriaceous, ovate-sagittate, the anterior lobe to about 75 by 70 cm and the posterior lobes to 1 m or more long.² ⁴</t>
+          <t>Massive pachycaul rhizomatous evergreen herb 3–4 m tall; rhizome dense, more or less without internodes, c. 40 cm thick with the leaf-base remains. Leaves several together; petioles stout, somewhat spreading, plain green, 1.3–2 m long and c. 12 cm thick towards the base, with crowded to scattered small prickles at the base and increasingly scattered prickles above, sheathing in the lower sixth or so, somewhat channelled above, filled with air cavities to 1 cm across, geniculate for several centimetres at the apex; blade ovate-sagittate, held more or less vertical with the posterior lobes down, somewhat irregularly wrinkled and bullate between the primary veins, to c. 2.25 m long by c. 1.2 m wide at the petiole insertion and somewhat wider behind it; anterior and posterior lobes about equal or the posterior somewhat longer; the costae massive, to 3 cm thick at the base, impressed above and very prominent beneath, the anterior costa with c. 10 robust primary lateral veins, the posterior costae diverging at 40–60° and naked in the sinus for c. 10 cm; posterior lobes with their outer sides overlapping each other; finer venation reticulate.⁶ Engler's description, from herbarium material, gave the petiole to 2.5 m, the coriaceous blade with the anterior lobe to about 75 by 70 cm and the posterior lobes to 1 m or more long, and Hay added that the blade and upper petiole are unarmed and the lower petiole armed with scattered straight spines.² ⁴</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Peduncle to 4.5 cm thick, smooth. Spathe ovate-lanceolate, long-acuminate, reddish brown, convolute below, c. 35 cm or more long and 8 cm across; spadix dark rose, 21 by 4 cm on a 2 cm stipe. Flowers 4–5-merous; anthers exserted from the perianth in a preserved fruiting spadix; ovary with several ovules. Fruiting spadix to 36 by 9 cm, with some 1,300 green ellipsoid berries 1.5 cm long, each holding up to five seeds; the seeds longitudinally crested like those of C. merkusii. By far the largest infructescence in the genus.² ⁴</t>
+          <t>Blooms solitary, but up to three or more in close succession, each separated by a foliage leaf; peduncle much shorter than the petioles, c. 50 cm long and 4.5 cm thick, unarmed or with a few scattered prickles, tinged brown, larger and plain green in fruit, inconspicuously geniculate near the apex. Spathe more or less canoe-shaped, erect, 35–50 cm long, convolute in the lower c. 8 cm, narrowed and acuminate in the upper third, greenish brown at the base and then burgundy-red to yellowish brown outside, cream to yellow with faintly purple-suffused streaks within. Spadix on a 2 cm stipe, stout, tapering-cylindric, 21–30 cm long and 4–5.5 cm thick below, blunt, dull brownish pink; florets bisexual, extremely numerous (over 2,000 to a spadix), rhomboid to hexagonal from above, c. 3 mm across; tepals 4–6, free, c. 3.5 mm long; stamens 4–6 with free filaments c. 1 mm long, the anthers partly exserted at male anthesis; pistil c. 4 mm, the stigma button-like and more or less sessile, the ovary unilocular with several ovules. Infructescence massive, deflected by the genicular zone near the top of the peduncle and accompanied by the marcescent spathe, the fruiting spadix 36–45 cm long and 9–11 cm thick; berries ellipsoid, c. 1.5 by 0.6 cm, their more or less pointed tips protruding from the tepals, dark green ripening yellow, with 1–5 seeds; seeds reniform, longitudinally crested, 5–6 mm long.⁶ Hay counted some 1,300 fruits on a preserved infructescence, by far the largest in the genus, and found the seeds crested like those of C. merkusii.⁴</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Lowland swamp forest of the Lorentz River, at 10–15 m.⁵</t>
+          <t>Open swampy areas with scattered sago palms (Metroxylon) and Campnosperma, and disturbed swamp forest with Campnosperma, Nauclea and Pandanus, at very low elevation, 10–15 m.⁵ ⁶</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1109,9 +1111,11 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1. Its 4–5-merous flowers, pluriovulate ovary and multi-seeded berries are unique in Cyrtosperma and led Engler to ally it with the African Lasiomorpha senegalensis; the marcescent spathe, the geniculate petiole and peduncle and the free filaments place it in Cyrtosperma proper, and the exserted anthers and crested seeds put it, tentatively, in the Merkusii group.⁴
-2. Hay &amp; Imran (2020) reported the species found again in Papua Province, in the same issue of Aroideana that described the second southern giant, C. timikense.⁶
-3. Now in cultivation: iNaturalist records from 2025 and 2026 include garden plants.³</t>
+          <t>1. Its 4–6-merous flowers, pluriovulate ovary and multi-seeded berries are unique in Cyrtosperma and led Engler to ally it with the African Lasiomorpha senegalensis; the marcescent spathe, the geniculate petiole and peduncle and the free filaments place it in Cyrtosperma proper, and the exserted anthers and crested seeds put it, tentatively, in the Merkusii group.⁴ ⁶
+2. Named by Engler in Engler &amp; Krause's account of the Araceae of the Lorentz expedition, from Versteeg's collections; the type locality's river has carried three names, Noord, Lorentz and Unir.² ⁶
+3. Hay &amp; Imran (2020) gave the first illustrations of the living plant, photographed by Imran near Timika, with an updated description a hundred and ten years after the protologue. They set it beside C. cuspidispathum as one of the two most gigantic New Guinea aroids, and in a note added in proof announced a third, C. timikense, described later in the same issue.⁶ ⁷
+4. The ripe berries protrude from the tepals but are not expelled; the "anthuriocarp", in which the expelled fruits hang from the spadix by the stripped inner epidermis of the tepals, is known in the genus only in C. cuspidispathum and, from Imran's observations near Timika, in C. hambalii.⁶
+5. Now in cultivation: iNaturalist records from 2025 and 2026 include garden plants.³</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1121,8 +1125,9 @@
 3. iNaturalist: Cyrtosperma giganteum. https://www.inaturalist.org/taxa/937778
 4. Hay, A. 1988. Cyrtosperma (Araceae) and its Old World allies. Blumea 33: 427–469. https://repository.naturalis.nl/pub/526134
 5. GBIF occurrence download for Cyrtosperma, 2026-09-05 (17 records). https://www.gbif.org/species/2871904
-6. Hay, A. &amp; Imran. 2020. Cyrtosperma giganteum Engl. found again in Papua Province, Indonesia. Aroideana 43(3–4): 4.
-7. Engler, A. 1911. Araceae-Lasioideae. Das Pflanzenreich IV.23C: 17. https://archive.org/details/daspflanzenreich48engluoft</t>
+6. Hay, A. &amp; Imran. 2020. Cyrtosperma giganteum Engl. (Araceae–Lasioideae) found again in Papua Province, Indonesia. Aroideana 43(3–4): 4–11.
+7. Hay, A. &amp; Imran. 2020. A third enormous New Guinea lasioid — Cyrtosperma timikense, a new species from southern Papua Province, Indonesia. Aroideana 43(3–4): 97–107.
+8. Engler, A. 1911. Araceae-Lasioideae. Das Pflanzenreich IV.23C: 17. https://archive.org/details/daspflanzenreich48engluoft</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1131,7 +1136,7 @@
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="7">
@@ -1239,7 +1244,7 @@
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>644</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1350,7 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>557</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1456,7 @@
         </is>
       </c>
       <c r="T9" s="2" t="n">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10">
@@ -1518,7 +1523,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Spathe broadly ovate, clasping in the lower fifth, c. 12 cm long and to 8 cm wide when flattened, deep reddish brown with yellow, widely reticulate venation that persists as a skeleton around the fruiting spadix; spadix with a 4 mm stipe adnate to the spathe, the fertile part c. 2.5 cm long and 5 mm wide. Flowers tetramerous; anthers not exserted from the tepals at male anthesis; stigmas raised 1–2 mm on the conical apex of the ovary. Fruit ovoid, capped by the style and stigma. Seed smooth.²</t>
+          <t>Spathe broadly ovate, clasping in the lower fifth, c. 12 cm long and to 8 cm wide when flattened, deep reddish brown with yellow, widely reticulate venation that persists as a skeleton around the fruiting spadix; spadix with a 4 mm stipe adnate to the spathe, the fertile part c. 2.5 cm long and 5 mm wide. Flowers tetramerous; anthers exserted from the tepals at male anthesis (Hay wrote in 1988 that they were not, from limited herbarium material, and corrected this from living plants in 2001); stigmas raised 1–2 mm on the conical apex of the ovary. Fruit ovoid, capped by the style and stigma. Seed smooth.²</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1540,7 +1545,8 @@
         <is>
           <t>1. The sole member of Hay's Carrii group: lower spathe convolute, flowers tetramerous, style conical and persisting on the fruit.²
 2. The net of yellow veins that remains as a skeleton around the fruiting spadix after the spathe tissue has gone is unique in the genus.²
-3. "Cyrtosperma carrii would seem to have horticultural potential", Hay wrote in 1988;² a cultivated plant was recorded on iNaturalist in 2025.³</t>
+3. "Cyrtosperma carrii would seem to have horticultural potential", Hay wrote in 1988;² a cultivated plant was recorded on iNaturalist in 2025.³
+4. Dearden &amp; Hay (2001) note that C. hambalii recalls this species in its dark spathe and exserted stamens, and record that the stamens of C. carrii are exserted at male anthesis, correcting the 1988 account.⁵</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1548,7 +1554,8 @@
           <t>1. Plants of the World Online, Royal Botanic Gardens, Kew — Cyrtosperma carrii. https://powo.science.kew.org/taxon/urn:lsid:ipni.org:names:935718-1
 2. Hay, A. 1988. Cyrtosperma (Araceae) and its Old World allies. Blumea 33: 427–469 — protologue, p. 450. https://repository.naturalis.nl/pub/526134
 3. iNaturalist: Cyrtosperma carrii. https://www.inaturalist.org/taxa/430921
-4. GBIF occurrence download for Cyrtosperma, 2026-09-05 (8 records). https://www.gbif.org/species/2871903</t>
+4. GBIF occurrence download for Cyrtosperma, 2026-09-05 (8 records). https://www.gbif.org/species/2871903
+5. Dearden, A. &amp; Hay, A. 2001. A new species of Cyrtosperma (Araceae) from West Papua. Aroideana 24: 102–104.</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1557,7 +1564,7 @@
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>456</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11">
@@ -1663,7 +1670,7 @@
         </is>
       </c>
       <c r="T11" s="2" t="n">
-        <v>462</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12">
@@ -1769,7 +1776,7 @@
         </is>
       </c>
       <c r="T12" s="2" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13">
@@ -1795,13 +1802,15 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>hero from inat/hambalii (six wild observations from Indonesian Papua, 2023–2026, four research grade); no type image online</t>
+          <t>hero from inat/hambalii (six wild observations from Indonesian Papua, 2023–2026, four research grade); the protologue's two photographs (flowering plant with the "rabbit's ears" leaves; inflorescence) are in Aroideana 24 on the Drive; no type image online</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Cyrtosperma hambalii A.Dearden &amp; A.Hay, published in Aroideana 24: 102–104 (2001), "A new species of Cyrtosperma (Araceae) from West Papua".
-⚠ Type and description not yet transcribed: the protologue is held on the Drive (Aroideana 24) and has not been read for this page.</t>
+          <t>Cyrtosperma hambalii A.Dearden &amp; A.Hay, published in Aroideana 24: 102–104 (2001), "A new species of Cyrtosperma (Araceae) from West Papua", with two photographs.
+Type: A. Hay &amp; A. Dearden s.n., 12 May 2001, cultivated at Redlynch, Cairns, Queensland, from a plant brought into the Freeport nursery at Timika from the vicinity of Timika, West Papua (original collection G.G. Hambali s.n.) (holotype NSW).²
+Diagnosis, translated from the Latin: differs from C. beccarianum in the shorter petiole, the very long spathe and the exserted stamens; from C. cuspidispathum in the much smaller plant, the shorter petiole, the very small anterior lobe of the leaf, the wholly erect spathe, the much shorter spadix and the exserted stamens.²
+From the protologue: Rhizomatous herb to c. 1 m tall. Stem condensed, subterranean. Leaves c. 4 bunched together; petiole erect, short, about half the length of the blade, c. 17 cm long, geniculate in the apical 1 cm, unarmed, dark olive brown at the base, mid green at the apex and olive green mottled olive brown between, sheathing in the lower third; blade sagittate, held with the posterior lobes erect and the anterior lobe pointing obliquely down, c. 32 cm long; anterior lobe much shorter than the posterior, narrowly triangular, 8 cm long and c. 2.5 cm wide where it meets the posterior lobes; posterior lobes rather narrowly elliptic, c. 23 by 7 cm, acuminate for 2 cm; costae very prominent beneath and impressed above, the anterior costa without primary veins and running sharply to the leaf tip, the posterior costae naked in the sinus for 5–8 mm with 5 or 6 primary lateral veins on each side diverging at c. 30°; finer venation a loose reticulum. Inflorescence solitary; peduncle much exceeding the petioles, 47 cm long, armed with scattered straight prickles, increasingly concentrated upwards, only in the distal 12 cm. Spathe erect, unarmed, with a prominent central ridge on the back, very long and slender, 53 cm long and 2.2 cm wide level with the spadix, then tapering, convolute at the base, the margins close together above, dark greenish brown with eight green vertical stripes outside and blackish within. Spadix much shorter than the spathe, cylindric, blunt, 6 by 0.8 cm, sessile; flowers hexamerous, c. 1.5 mm across; anthers exserted from the tepals at male anthesis. Fruit unknown.²</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1826,22 +1835,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>South-western New Guinea; iNaturalist records are from Indonesian Papua.³ Living plants are grown at the Bogor Botanic Gardens, where a Sorong collection long labelled with this name proved to be C. prasinispathum.⁵</t>
+          <t>Endemic to New Guinea and, in the protologue, known only from the vicinity of Timika in southern West Papua, now the Mimika Regency of Central Papua Province.² iNaturalist records come from the Mimika lowlands and from Sorong at the western tip of the Bird's Head;³ the Sorong plants long grown at Bogor under this name proved to be C. prasinispathum, so the Sorong records deserve a check.⁵ Living plants are grown at the Bogor Botanic Gardens.⁵</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue. What the sources in hand show: a plant close enough to C. prasinispathum to have been confused with it at Bogor; a recent figure describes its characteristic "rabbit-ear" leaves.⁵ ⁶</t>
+          <t>A rhizomatous herb to about 1 m tall with a condensed underground stem and about four leaves bunched together. The petiole is unusually short, about half the length of the blade (c. 17 cm), unarmed, mottled olive, sheathing in its lower third and geniculate at the tip. The blade is sagittate, c. 32 cm long, and is held with the two narrowly elliptic posterior lobes (c. 23 by 7 cm) pointing up and the much reduced, narrowly triangular anterior lobe (8 by 2.5 cm) pointing obliquely down, which gives the plant its "rabbit's ears" look.² Plants near Timika have since been seen with ripe berries expelled from the florets and hanging on the spadix, the "anthuriocarp" otherwise known in the genus only in C. cuspidispathum.⁷</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue.</t>
+          <t>Inflorescence solitary, held high above the leaves on a peduncle 47 cm long that is prickly only in its distal 12 cm. Spathe perfectly erect, very long and slender, 53 cm long and 2.2 cm wide at the level of the spadix, tapering above, convolute at the base, with a prominent central ridge on the back, dark greenish brown with eight green stripes outside and blackish inside. Spadix sessile, cylindric, blunt, only 6 by 0.8 cm; flowers hexamerous, c. 1.5 mm across, the anthers exserted from the tepals at male anthesis. Fruit unknown in 2001;² berries have since been seen on plants near Timika.⁷</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue; the iNaturalist records are lowland.³</t>
+          <t>Habitat not recorded in the protologue;² the iNaturalist records are lowland, from the swampy coastal plain around Timika and from Sorong.³</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1851,13 +1860,16 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Presumably for Gregori Garnadi Hambali, the Indonesian aroid specialist at Bogor; ⚠ to be confirmed from the protologue.</t>
+          <t>Named for Gregory G. Hambali, whose collecting in West Papua produced the species, in acknowledgement of his long and expert contribution to Indonesian botany and horticulture and of his part in the rediscovery of the closely related Lasia concinna.²</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>1. Hariri et al. (2024) compare their new C. prasinispathum with the Bogor plants that had carried this name and figure a leaf of C. hambalii beside it (their Fig. 1J).⁵
-2. Six wild observations on iNaturalist, four of them research grade, are currently the best photographs of the species available to the build.³</t>
+          <t>1. Closest to the rheophytic C. beccarianum in leaf shape, from which it differs in the short petioles, the extremely elongate dark greenish brown spathe (ovate, wide open and generally white in C. beccarianum), the hexamerous flowers (tetramerous there) and the exserted stamens (not exserted there). The very long spathe recalls C. cuspidispathum, a far larger plant whose spathe is reflexed to dangling in its distal part, whose stamens are not exserted, whose leaves have well-developed anterior lobes with the posterior lobes held down, and whose petioles carry upturned prickles. In spathe colour and exserted stamens it recalls C. carrii of Central Province, which has extremely prickly leaves with well-developed anterior lobes and a squat, open spathe.²
+2. The authors correct Hay's 1988 statement that the stamens of C. carrii are not exserted: it rested on limited herbarium material, and living plants show them exserted.² ⁶
+3. The sheath reaching a third of the way up the petiole is unusual in the genus, though it may simply be that the rest of the petiole is foreshortened. The species keys out in Hay's 1988 key at a new couplet 3a, leaf blade with the anterior lobe much reduced and narrowly triangular and the posterior lobes erect; the genus then stood at twelve species.² ⁶
+4. Hariri et al. (2024) compare their new C. prasinispathum with the Bogor plants that had carried this name and figure a leaf of C. hambalii beside it (their Fig. 1J).⁵
+5. Six wild observations on iNaturalist, four of them research grade, are the best photographs of the species available to the build; the protologue's two figures show the flowering plant and the inflorescence.² ³</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -1867,16 +1879,17 @@
 3. iNaturalist: Cyrtosperma hambalii. https://www.inaturalist.org/taxa/937776
 4. GBIF occurrence download for Cyrtosperma, 2026-09-05 (1 record). https://www.gbif.org/species/2871917
 5. Hariri, M.R. et al. 2024. Cyrtosperma prasinispathum: a new fascinating Aroid species from Papua, Indonesia. Webbia 79(2): 291–294. https://doi.org/10.36253/jopt-16076
-6. ResearchGate figure, publication 375336461 (2023): Cyrtosperma hambalii, flowering plant showing characteristic "rabbit ear" leaves.</t>
+6. Hay, A. 1988. Cyrtosperma (Araceae) and its Old World allies. Blumea 33: 427–469. https://repository.naturalis.nl/pub/526134
+7. Hay, A. &amp; Imran. 2020. Cyrtosperma giganteum Engl. (Araceae–Lasioideae) found again in Papua Province, Indonesia. Aroideana 43(3–4): 4–11 (note added in proof).</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>PROTOLOGUE; SPECIES DESCRIPTION; INFLORESCENCE; ECOLOGY; ETYMOLOGY</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T13" s="2" t="n">
-        <v>333</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="14">
@@ -1902,13 +1915,15 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>none in the pack; no iNaturalist or GBIF record; seed is offered commercially, so cultivated plants exist</t>
+          <t>none in the pack; the protologue's seven photographs by Imran, all from the type population (Aroideana 43(3–4), on the Drive), are the only published images; no iNaturalist or GBIF record; seed is offered commercially, so cultivated plants exist</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Cyrtosperma timikense Imran &amp; A.Hay, published in Aroideana 43(3–4): 97–107 (2020), "A third enormous New Guinea lasioid — Cyrtosperma timikense, a new species from southern Papua Province, Indonesia".
-⚠ Type and description not yet transcribed: the protologue is held on the Drive (Aroideana 43) and has not been read for this page. The published abstract states that the species, from the Mimika Regency of Papua Province, is distinguished from C. cuspidispathum, which it most resembles.²</t>
+          <t>Cyrtosperma timikense Imran &amp; A.Hay, published in Aroideana 43(3–4): 97–107 (2020), "A third enormous New Guinea lasioid — Cyrtosperma timikense, a new species from southern Papua Province, Indonesia", with seven photographs.
+Type: Imran s.n., 28 October 2020, Indonesia, Papua Province, Mimika Regency, near Timika, 4°39'47"S 136°49'36"E (holotype MAN; isotype BO, to be distributed).²
+Diagnosis: resembles C. cuspidispathum in its very elongate spathe, gigantic size and small prickles, but differs in its strongly clumping habit, the somewhat angular distal part of the petiole and geniculum, the much narrower spathe with a somewhat inflated green basal portion, the stamens exserted from the tepals at male anthesis, the fruits apparently not expelled from the spadix at maturity, and the rather elaborately crested seeds, two to a berry.²
+From the protologue: Massive, evergreen, strongly clump-forming herb to c. 3 m tall; stem a condensed subterranean rhizome 25–40 cm across including the leaf bases; leaves c. 8 per crown. Petioles held close together and vertical in the lower half and then weakly spreading, 2–2.5 m long, sheathing in the lower 30–40 cm with the wings of the sheath papery and then degrading to sparse fibres, dark grey-green densely and obliquely streaked buff in the lower half, bright green and somewhat angular in section above, sparsely armed with very small obliquely down-pointing prickles that follow the streaks below and become scattered and upturned above, conspicuously geniculate for c. 7 cm at the apex. Blades broadly triangular-sagittate, held with the anterior lobe up and the posterior lobes down, 1–1.5 m long, unarmed and rather small for the size of the plant; anterior lobe 40–50 cm long and 50–60 cm wide at the petiole insertion; posterior lobes 60–90 cm long; posterior costae diverging at c. 110° and naked in the sinus for c. 8 cm; anterior costa very prominent beneath, with about nine primary lateral veins on each side diverging at 60–70° and arching up to the margin, mostly with one or two secondary veins in the outer third of the blade; finer venation reticulate. Blooms solitary or up to three in succession; peduncles somewhat shorter than the petioles, 1.5–2.3 m long, densely armed throughout with small, mostly ungrouped, mostly upturned prickles like those of the petioles. Spathe to c. 80 cm long, somewhat convolute, green and slightly inflated in the basal 7–11 cm, giving the faint impression of a distinct lower spathe and limb, then narrowly canoe-shaped and very long-attenuate, dull purple with faint paler streaks within and slightly paler veins without, marcescent after anthesis and mostly disintegrated by fruiting. Spadix on a sparsely and minutely prickly stipe 2–3 cm long, tapering-cylindric, c. 20 cm long at female anthesis and enlarging to c. 26 cm during male anthesis; florets with six free tepals and six stamens, the anthers exserted from the tepals at male anthesis; pistil apparently unilocular and two-ovulate, the stigma discoid, sessile, almost as wide as the ovary. Infructescence at first erect, later deflected by pulvinar activity near the top of the peduncle, to c. 40 cm long; berries ripening red-orange, depressed-globose and weakly lobed with the darkened stigma remains at the top, apparently not expelled from the spadix, mostly two-seeded with one larger and one smaller (perhaps non-viable) seed; seeds reniform, ornamented with prominently lobed crests, c. 0.5 or c. 1 cm long.²</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1931,20 +1946,24 @@
           <t>New Guinea: New Guinea (Papua Province, Mimika Regency).¹ ²</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Known only from the population near Timika from which the type was gathered, some 500 km west of the nearest southern record of C. cuspidispathum and on the far side of the Central Cordillera from the Jayapura records of that species.²</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue. The title places it with C. cuspidispathum and C. giganteum as the third "enormous" lasioid of New Guinea, so a plant of several metres.²</t>
+          <t>A massive, evergreen, vigorously clump-forming herb to about 3 m tall, the base of a large clump forming a thicket of crowns, each of about eight leaves on a condensed underground rhizome 25–40 cm across. Petioles 2–2.5 m long, vertical and close together below and weakly spreading above, dark grey-green streaked buff in the lower half and bright green and somewhat angular above, sparsely armed with very small prickles and conspicuously geniculate at the apex; blades broadly triangular-sagittate, 1–1.5 m long, unarmed and rather small for the plant, held with the anterior lobe up and the posterior lobes down.²</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue; its resemblance to C. cuspidispathum suggests a long spathe with a twisted tip.²</t>
+          <t>Blooms solitary or up to three in succession, on densely prickly peduncles 1.5–2.3 m long. Spathe to about 80 cm long, its green, slightly inflated, convolute base giving the faint impression of a distinct lower spathe, the rest narrowly canoe-shaped, dull purple, indistinctly streaked and drawn out into a very long, backward-arching tip. Spadix stipitate, tapering, 20–26 cm long; flowers hexamerous with the anthers exserted at male anthesis. Infructescence to c. 40 cm, deflected as it ripens; berries red-orange, depressed-globose, weakly lobed, apparently not expelled from the spadix, mostly two-seeded with one seed larger than the other; seeds reniform with prominently lobed crests.²</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>⚠ To be taken from the protologue; southern Papua lowlands.²</t>
+          <t>Open degraded swamp forest at about 8 m altitude.²</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1954,14 +1973,16 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Of Timika, the town of the Mimika Regency in southern Papua, the type region.</t>
+          <t>For Timika, the capital of the Mimika Regency in Indonesian Papua, near which the species was found.²</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1. Described in the same issue of Aroideana as the rediscovery of C. giganteum and the note on C. johnstonii; one PDF covers all three.² ⁴ ⁵
-2. Hariri et al. (2024) count it among the 14 species known before C. prasinispathum.⁶
-3. Seed is offered by at least one European seed merchant under this name, so the species is entering cultivation; no photograph has yet reached iNaturalist or GBIF.³ ⚠</t>
+          <t>1. The third of the enormous New Guinea cyrtospermas, with C. cuspidispathum and C. giganteum, and the most like C. cuspidispathum in its size, its long-attenuate, basally convolute spathe and its very numerous small prickles. It differs in being vigorously clump-forming where C. cuspidispathum is usually solitary in the wild, in producing a few blooms in succession, in the much narrower spathe with only a small inflated green base (much more extensively convolute and vase-shaped, purple-brown, in C. cuspidispathum), reaching about 80 cm against 1.25 m, more indistinctly streaked and lacking the contrasting yellowish veins, in the exserted anthers, in the depressed-globose berries that stay on the spadix (rounder, and expelled anthurium-like, in C. cuspidispathum) and in the conspicuously crested seeds (barely ornamented in C. cuspidispathum).²
+2. Discovered by Imran in the same part of southern Papua where the two authors had just re-found C. giganteum; the discovery is announced in a note added in proof to that paper, which puts the genus at fourteen species, eight of them on New Guinea.⁴
+3. Described in the same issue of Aroideana as the rediscovery of C. giganteum and the note on C. johnstonii.² ⁴ ⁵
+4. Hariri et al. (2024) count it among the fourteen species known before C. prasinispathum.⁶
+5. Seed is offered by at least one European seed merchant under this name, so the species is entering cultivation; no photograph has yet reached iNaturalist or GBIF, and the protologue's figures are the only published images.² ³ ⚠</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1969,18 +1990,18 @@
           <t>1. Plants of the World Online, Royal Botanic Gardens, Kew — Cyrtosperma timikense. https://powo.science.kew.org/taxon/urn:lsid:ipni.org:names:77214865-1
 2. Hay, A. &amp; Imran. 2020. A third enormous New Guinea lasioid — Cyrtosperma timikense, a new species from southern Papua Province, Indonesia. Aroideana 43(3–4): 97–107 — protologue.
 3. GBIF: no occurrence records (2026-09-05).
-4. Hay, A. &amp; Imran. 2020. Cyrtosperma giganteum Engl. found again in Papua Province, Indonesia. Aroideana 43(3–4): 4.
-5. Hay, A. 2020. Notes on the typification, origin, and fertility of Cyrtosperma johnstonii. Aroideana 43(3–4): 108.
+4. Hay, A. &amp; Imran. 2020. Cyrtosperma giganteum Engl. (Araceae–Lasioideae) found again in Papua Province, Indonesia. Aroideana 43(3–4): 4–11.
+5. Hay, A. 2020. Notes on the typification, origin, and fertility of Cyrtosperma johnstonii (Araceae–Lasioideae). Aroideana 43(3–4): 108–117.
 6. Hariri, M.R. et al. 2024. Cyrtosperma prasinispathum: a new fascinating Aroid species from Papua, Indonesia. Webbia 79(2): 291–294. https://doi.org/10.36253/jopt-16076</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>PROTOLOGUE; SPECIES DESCRIPTION; INFLORESCENCE; ECOLOGY; NOTES</t>
+          <t>NOTES</t>
         </is>
       </c>
       <c r="T14" s="2" t="n">
-        <v>366</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="15">
@@ -2083,7 +2104,7 @@
         </is>
       </c>
       <c r="T15" s="2" t="n">
-        <v>350</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
@@ -2191,7 +2212,7 @@
         </is>
       </c>
       <c r="T16" s="2" t="n">
-        <v>582</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -2205,10 +2226,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2316,7 +2337,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Accepted subspecies/varieties (none in Cyrtosperma)</t>
+          <t>Accepted subspecies/varieties</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2452,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>⚠</t>
+          <t>FIELDS STILL OPEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A field marked ⚠ is one the sources in hand could not fill (Aroideana papers on the Drive; Phytotaxa paywalled; no photograph found)</t>
+          <t>Fields marked ⚠ in the draft: the sources in hand could not fill them</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WORDS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Word count of the draft</t>
         </is>
       </c>
     </row>
